--- a/Oil_Data_Consolidated_updated.xlsx
+++ b/Oil_Data_Consolidated_updated.xlsx
@@ -19,16 +19,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +50,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -419,53 +433,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G227"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Fuel Type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Closing Stock</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Offtake</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Tonga Power Offtake</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="3" t="n">
         <v>46098</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,19 +492,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="3" t="n">
         <v>46098</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -503,17 +515,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="3" t="n">
         <v>46099</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -526,19 +535,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="3" t="n">
         <v>46099</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -551,17 +558,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="3" t="n">
         <v>46100</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -574,19 +578,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="3" t="n">
         <v>46100</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -599,17 +601,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="3" t="n">
         <v>46101</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -622,19 +621,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="3" t="n">
         <v>46101</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -647,17 +644,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="3" t="n">
         <v>46102</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -670,19 +664,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="3" t="n">
         <v>46102</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -695,17 +687,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="3" t="n">
         <v>46103</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -718,19 +707,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="3" t="n">
         <v>46103</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -743,17 +730,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="3" t="n">
         <v>46104</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -766,19 +750,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="3" t="n">
         <v>46104</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -791,17 +773,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="3" t="n">
         <v>46105</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -814,19 +793,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>0</v>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="3" t="n">
         <v>46105</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -839,17 +816,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="3" t="n">
         <v>46106</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -862,19 +836,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>0</v>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="3" t="n">
         <v>46106</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -887,17 +859,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="3" t="n">
         <v>46107</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -910,19 +879,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
         <v>0</v>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="3" t="n">
         <v>46107</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -935,17 +902,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="3" t="n">
         <v>46108</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -958,19 +922,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
         <v>0</v>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="3" t="n">
         <v>46108</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -983,17 +945,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="3" t="n">
         <v>46109</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1006,19 +965,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
         <v>0</v>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="3" t="n">
         <v>46109</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1031,17 +988,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="3" t="n">
         <v>46110</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1054,19 +1008,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="3" t="n">
         <v>46110</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1079,17 +1031,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="3" t="n">
         <v>46111</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1102,19 +1051,17 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
         <v>0</v>
       </c>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="3" t="n">
         <v>46111</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1127,17 +1074,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="3" t="n">
         <v>46112</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1154,19 +1098,19 @@
         <v>1901677</v>
       </c>
       <c r="F30" t="n">
-        <v>84910</v>
+        <v>20000</v>
       </c>
       <c r="G30" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="3" t="n">
         <v>46112</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1185,15 +1129,17 @@
       <c r="F31" t="n">
         <v>6000</v>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1210,19 +1156,19 @@
         <v>1780336</v>
       </c>
       <c r="F32" t="n">
-        <v>121010</v>
+        <v>68000</v>
       </c>
       <c r="G32" t="n">
         <v>68000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1241,15 +1187,17 @@
       <c r="F33" t="n">
         <v>21400</v>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="3" t="n">
         <v>46114</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1266,19 +1214,19 @@
         <v>1637854</v>
       </c>
       <c r="F34" t="n">
-        <v>142000</v>
+        <v>80000</v>
       </c>
       <c r="G34" t="n">
         <v>80000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="3" t="n">
         <v>46114</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1297,15 +1245,17 @@
       <c r="F35" t="n">
         <v>12000</v>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="3" t="n">
         <v>46115</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1329,12 +1279,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="3" t="n">
         <v>46115</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1353,15 +1303,17 @@
       <c r="F37" t="n">
         <v>0</v>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="3" t="n">
         <v>46116</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1385,12 +1337,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="3" t="n">
         <v>46116</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1409,15 +1361,17 @@
       <c r="F39" t="n">
         <v>18000</v>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="3" t="n">
         <v>46117</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1441,12 +1395,12 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="3" t="n">
         <v>46117</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1465,15 +1419,17 @@
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="3" t="n">
         <v>46118</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1497,12 +1453,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="3" t="n">
         <v>46118</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1521,15 +1477,17 @@
       <c r="F43" t="n">
         <v>0</v>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="3" t="n">
         <v>46119</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1542,19 +1500,23 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>1437030</v>
+      </c>
       <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
+        <v>56500</v>
+      </c>
+      <c r="G44" t="n">
+        <v>40000</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="3" t="n">
         <v>46119</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1567,17 +1529,23 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>617312</v>
+      </c>
+      <c r="F45" t="n">
+        <v>31000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="3" t="n">
         <v>46120</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1590,19 +1558,23 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>1318903</v>
+      </c>
       <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
+        <v>120000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>120000</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="3" t="n">
         <v>46120</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1615,17 +1587,23 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>617312</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="3" t="n">
         <v>46121</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1638,19 +1616,23 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>1256089</v>
+      </c>
       <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
+        <v>63000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>60000</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="3" t="n">
         <v>46121</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1663,17 +1645,23 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>603447</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="3" t="n">
         <v>46122</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1686,19 +1674,23 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>1164376</v>
+      </c>
       <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
+        <v>100000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>100000</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="3" t="n">
         <v>46122</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1711,17 +1703,23 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>563813</v>
+      </c>
+      <c r="F51" t="n">
+        <v>43000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="3" t="n">
         <v>46123</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1734,19 +1732,23 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>1164376</v>
+      </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="3" t="n">
         <v>46123</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1759,17 +1761,23 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>563284</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="3" t="n">
         <v>46124</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1782,19 +1790,23 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>1164376</v>
+      </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="3" t="n">
         <v>46124</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1807,17 +1819,23 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>563284</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="3" t="n">
         <v>46125</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1830,19 +1848,23 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>998251</v>
+      </c>
       <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="inlineStr"/>
+        <v>165830</v>
+      </c>
+      <c r="G56" t="n">
+        <v>165830</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="3" t="n">
         <v>46125</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1855,17 +1877,23 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>524021</v>
+      </c>
+      <c r="F57" t="n">
+        <v>38810</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="3" t="n">
         <v>46126</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1878,19 +1906,23 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>877834</v>
+      </c>
       <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="inlineStr"/>
+        <v>120000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>120000</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="3" t="n">
         <v>46126</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1903,17 +1935,23 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>524021</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="3" t="n">
         <v>46127</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1926,19 +1964,23 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>836660</v>
+      </c>
       <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="inlineStr"/>
+        <v>39500</v>
+      </c>
+      <c r="G60" t="n">
+        <v>20000</v>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="3" t="n">
         <v>46127</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1951,17 +1993,23 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>491471</v>
+      </c>
+      <c r="F61" t="n">
+        <v>32200</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="3" t="n">
         <v>46128</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1974,19 +2022,23 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>734794</v>
+      </c>
       <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="inlineStr"/>
+        <v>100000</v>
+      </c>
+      <c r="G62" t="n">
+        <v>100000</v>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="3" t="n">
         <v>46128</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1999,17 +2051,23 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>491471</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="3" t="n">
         <v>46129</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2022,19 +2080,23 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>533261</v>
+      </c>
       <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
+        <v>201010</v>
+      </c>
+      <c r="G64" t="n">
+        <v>201010</v>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="3" t="n">
         <v>46129</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2047,17 +2109,23 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>463521</v>
+      </c>
+      <c r="F65" t="n">
+        <v>27200</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="3" t="n">
         <v>46098</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2076,15 +2144,14 @@
       <c r="F66" t="n">
         <v>77500</v>
       </c>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="3" t="n">
         <v>46098</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2103,15 +2170,14 @@
       <c r="F67" t="n">
         <v>38600</v>
       </c>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="3" t="n">
         <v>46098</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2130,15 +2196,14 @@
       <c r="F68" t="n">
         <v>55200</v>
       </c>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="3" t="n">
         <v>46099</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2157,15 +2222,14 @@
       <c r="F69" t="n">
         <v>55300</v>
       </c>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="3" t="n">
         <v>46099</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2184,15 +2248,14 @@
       <c r="F70" t="n">
         <v>200</v>
       </c>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="3" t="n">
         <v>46099</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2211,15 +2274,14 @@
       <c r="F71" t="n">
         <v>70600</v>
       </c>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="3" t="n">
         <v>46100</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2238,15 +2300,14 @@
       <c r="F72" t="n">
         <v>86600</v>
       </c>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="3" t="n">
         <v>46100</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2265,15 +2326,14 @@
       <c r="F73" t="n">
         <v>0</v>
       </c>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="3" t="n">
         <v>46100</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2292,15 +2352,14 @@
       <c r="F74" t="n">
         <v>75200</v>
       </c>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="3" t="n">
         <v>46101</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2319,15 +2378,14 @@
       <c r="F75" t="n">
         <v>67100</v>
       </c>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="3" t="n">
         <v>46101</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2346,15 +2404,14 @@
       <c r="F76" t="n">
         <v>43800</v>
       </c>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="3" t="n">
         <v>46101</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2373,15 +2430,14 @@
       <c r="F77" t="n">
         <v>113200</v>
       </c>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="3" t="n">
         <v>46102</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2400,15 +2456,14 @@
       <c r="F78" t="n">
         <v>0</v>
       </c>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="3" t="n">
         <v>46102</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2427,15 +2482,14 @@
       <c r="F79" t="n">
         <v>0</v>
       </c>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="3" t="n">
         <v>46102</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2454,15 +2508,14 @@
       <c r="F80" t="n">
         <v>0</v>
       </c>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="3" t="n">
         <v>46103</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2481,15 +2534,14 @@
       <c r="F81" t="n">
         <v>0</v>
       </c>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="3" t="n">
         <v>46103</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2508,15 +2560,14 @@
       <c r="F82" t="n">
         <v>0</v>
       </c>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="3" t="n">
         <v>46103</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2535,15 +2586,14 @@
       <c r="F83" t="n">
         <v>0</v>
       </c>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="3" t="n">
         <v>46104</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2562,15 +2612,14 @@
       <c r="F84" t="n">
         <v>48800</v>
       </c>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="3" t="n">
         <v>46104</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2589,15 +2638,14 @@
       <c r="F85" t="n">
         <v>200</v>
       </c>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="3" t="n">
         <v>46104</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2616,15 +2664,14 @@
       <c r="F86" t="n">
         <v>99540</v>
       </c>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="3" t="n">
         <v>46105</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2643,15 +2690,14 @@
       <c r="F87" t="n">
         <v>27800</v>
       </c>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="3" t="n">
         <v>46105</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2670,15 +2716,14 @@
       <c r="F88" t="n">
         <v>46600</v>
       </c>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="3" t="n">
         <v>46105</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2697,15 +2742,14 @@
       <c r="F89" t="n">
         <v>59800</v>
       </c>
-      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="3" t="n">
         <v>46106</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2724,15 +2768,14 @@
       <c r="F90" t="n">
         <v>30000</v>
       </c>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="3" t="n">
         <v>46106</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2751,15 +2794,14 @@
       <c r="F91" t="n">
         <v>2400</v>
       </c>
-      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="3" t="n">
         <v>46106</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2778,15 +2820,14 @@
       <c r="F92" t="n">
         <v>51500</v>
       </c>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="3" t="n">
         <v>46107</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2805,15 +2846,14 @@
       <c r="F93" t="n">
         <v>26900</v>
       </c>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="3" t="n">
         <v>46107</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2832,15 +2872,14 @@
       <c r="F94" t="n">
         <v>18700</v>
       </c>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="3" t="n">
         <v>46107</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2859,15 +2898,14 @@
       <c r="F95" t="n">
         <v>63300</v>
       </c>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="3" t="n">
         <v>46108</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2886,15 +2924,14 @@
       <c r="F96" t="n">
         <v>43500</v>
       </c>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="3" t="n">
         <v>46108</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2913,15 +2950,14 @@
       <c r="F97" t="n">
         <v>400</v>
       </c>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="3" t="n">
         <v>46108</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2940,15 +2976,14 @@
       <c r="F98" t="n">
         <v>92400</v>
       </c>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="3" t="n">
         <v>46109</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2967,15 +3002,14 @@
       <c r="F99" t="n">
         <v>0</v>
       </c>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="3" t="n">
         <v>46109</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2994,15 +3028,14 @@
       <c r="F100" t="n">
         <v>0</v>
       </c>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="3" t="n">
         <v>46109</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3021,15 +3054,14 @@
       <c r="F101" t="n">
         <v>0</v>
       </c>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="3" t="n">
         <v>46110</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3048,15 +3080,14 @@
       <c r="F102" t="n">
         <v>0</v>
       </c>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="3" t="n">
         <v>46110</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3075,15 +3106,14 @@
       <c r="F103" t="n">
         <v>0</v>
       </c>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="3" t="n">
         <v>46110</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3102,15 +3132,14 @@
       <c r="F104" t="n">
         <v>0</v>
       </c>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="3" t="n">
         <v>46111</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3129,15 +3158,14 @@
       <c r="F105" t="n">
         <v>120400</v>
       </c>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="3" t="n">
         <v>46111</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3156,15 +3184,14 @@
       <c r="F106" t="n">
         <v>10200</v>
       </c>
-      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="3" t="n">
         <v>46111</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3183,15 +3210,14 @@
       <c r="F107" t="n">
         <v>143450</v>
       </c>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="3" t="n">
         <v>46112</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3210,15 +3236,14 @@
       <c r="F108" t="n">
         <v>157300</v>
       </c>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="3" t="n">
         <v>46112</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3237,15 +3262,14 @@
       <c r="F109" t="n">
         <v>46000</v>
       </c>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="3" t="n">
         <v>46112</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3264,15 +3288,14 @@
       <c r="F110" t="n">
         <v>158100</v>
       </c>
-      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3291,15 +3314,14 @@
       <c r="F111" t="n">
         <v>10000</v>
       </c>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3318,15 +3340,14 @@
       <c r="F112" t="n">
         <v>23700</v>
       </c>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3345,15 +3366,14 @@
       <c r="F113" t="n">
         <v>5400</v>
       </c>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="3" t="n">
         <v>46114</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3372,15 +3392,14 @@
       <c r="F114" t="n">
         <v>34400</v>
       </c>
-      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="3" t="n">
         <v>46114</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3399,15 +3418,14 @@
       <c r="F115" t="n">
         <v>56300</v>
       </c>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="3" t="n">
         <v>46114</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3426,15 +3444,14 @@
       <c r="F116" t="n">
         <v>127700</v>
       </c>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="3" t="n">
         <v>46115</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3453,15 +3470,14 @@
       <c r="F117" t="n">
         <v>0</v>
       </c>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="3" t="n">
         <v>46115</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3480,15 +3496,14 @@
       <c r="F118" t="n">
         <v>0</v>
       </c>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="3" t="n">
         <v>46115</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3507,15 +3522,14 @@
       <c r="F119" t="n">
         <v>0</v>
       </c>
-      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="3" t="n">
         <v>46116</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3534,15 +3548,14 @@
       <c r="F120" t="n">
         <v>0</v>
       </c>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="3" t="n">
         <v>46116</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3561,15 +3574,14 @@
       <c r="F121" t="n">
         <v>0</v>
       </c>
-      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="3" t="n">
         <v>46116</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3588,15 +3600,14 @@
       <c r="F122" t="n">
         <v>0</v>
       </c>
-      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="3" t="n">
         <v>46117</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3615,15 +3626,14 @@
       <c r="F123" t="n">
         <v>0</v>
       </c>
-      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="3" t="n">
         <v>46117</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3642,15 +3652,14 @@
       <c r="F124" t="n">
         <v>0</v>
       </c>
-      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="3" t="n">
         <v>46117</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3669,15 +3678,14 @@
       <c r="F125" t="n">
         <v>0</v>
       </c>
-      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="3" t="n">
         <v>46118</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3696,15 +3704,14 @@
       <c r="F126" t="n">
         <v>0</v>
       </c>
-      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="3" t="n">
         <v>46118</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3723,15 +3730,14 @@
       <c r="F127" t="n">
         <v>0</v>
       </c>
-      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="3" t="n">
         <v>46118</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3750,15 +3756,14 @@
       <c r="F128" t="n">
         <v>0</v>
       </c>
-      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="3" t="n">
         <v>46119</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3782,12 +3787,12 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="3" t="n">
         <v>46119</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3811,12 +3816,12 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="3" t="n">
         <v>46119</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3840,12 +3845,12 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="3" t="n">
         <v>46120</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3869,12 +3874,12 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="3" t="n">
         <v>46120</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3898,12 +3903,12 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="3" t="n">
         <v>46120</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3927,12 +3932,12 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="3" t="n">
         <v>46121</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3956,12 +3961,12 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="3" t="n">
         <v>46121</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3985,12 +3990,12 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="3" t="n">
         <v>46121</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4014,12 +4019,12 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="3" t="n">
         <v>46122</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4043,12 +4048,12 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="3" t="n">
         <v>46122</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4072,12 +4077,12 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="3" t="n">
         <v>46122</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4101,12 +4106,12 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="3" t="n">
         <v>46123</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4130,12 +4135,12 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="3" t="n">
         <v>46123</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4159,12 +4164,12 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="3" t="n">
         <v>46123</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4188,12 +4193,12 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="3" t="n">
         <v>46124</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4217,12 +4222,12 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="3" t="n">
         <v>46124</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4246,12 +4251,12 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="3" t="n">
         <v>46124</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4275,12 +4280,12 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="3" t="n">
         <v>46125</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4293,17 +4298,14 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="3" t="n">
         <v>46125</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4316,17 +4318,14 @@
           <t>Kerosene</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="3" t="n">
         <v>46125</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4339,17 +4338,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="3" t="n">
         <v>46126</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4362,17 +4358,14 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="3" t="n">
         <v>46126</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4385,17 +4378,14 @@
           <t>Kerosene</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="3" t="n">
         <v>46126</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4408,17 +4398,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="3" t="n">
         <v>46127</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4431,17 +4418,14 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="3" t="n">
         <v>46127</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4454,17 +4438,14 @@
           <t>Kerosene</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="3" t="n">
         <v>46127</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4477,17 +4458,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="3" t="n">
         <v>46128</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4500,17 +4478,14 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="3" t="n">
         <v>46128</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4523,17 +4498,14 @@
           <t>Kerosene</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="3" t="n">
         <v>46128</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4546,17 +4518,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="3" t="n">
         <v>46129</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4569,17 +4538,14 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="3" t="n">
         <v>46129</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4592,17 +4558,14 @@
           <t>Kerosene</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="3" t="n">
         <v>46129</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4615,17 +4578,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="3" t="n">
         <v>46098</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4644,15 +4604,14 @@
       <c r="F162" t="n">
         <v>7000</v>
       </c>
-      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="3" t="n">
         <v>46098</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4671,15 +4630,14 @@
       <c r="F163" t="n">
         <v>18500</v>
       </c>
-      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="3" t="n">
         <v>46099</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4698,15 +4656,14 @@
       <c r="F164" t="n">
         <v>5200</v>
       </c>
-      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="3" t="n">
         <v>46099</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4725,15 +4682,14 @@
       <c r="F165" t="n">
         <v>6000</v>
       </c>
-      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="3" t="n">
         <v>46100</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4752,15 +4708,14 @@
       <c r="F166" t="n">
         <v>10250</v>
       </c>
-      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="3" t="n">
         <v>46100</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4779,15 +4734,14 @@
       <c r="F167" t="n">
         <v>16000</v>
       </c>
-      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="3" t="n">
         <v>46101</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4806,15 +4760,14 @@
       <c r="F168" t="n">
         <v>4000</v>
       </c>
-      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="3" t="n">
         <v>46101</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4833,15 +4786,14 @@
       <c r="F169" t="n">
         <v>4000</v>
       </c>
-      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="3" t="n">
         <v>46102</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4860,15 +4812,14 @@
       <c r="F170" t="n">
         <v>0</v>
       </c>
-      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="3" t="n">
         <v>46102</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4887,15 +4838,14 @@
       <c r="F171" t="n">
         <v>0</v>
       </c>
-      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="3" t="n">
         <v>46103</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4914,15 +4864,14 @@
       <c r="F172" t="n">
         <v>0</v>
       </c>
-      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="3" t="n">
         <v>46103</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4941,15 +4890,14 @@
       <c r="F173" t="n">
         <v>0</v>
       </c>
-      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="3" t="n">
         <v>46104</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4968,15 +4916,14 @@
       <c r="F174" t="n">
         <v>17000</v>
       </c>
-      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="3" t="n">
         <v>46104</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4995,15 +4942,14 @@
       <c r="F175" t="n">
         <v>19000</v>
       </c>
-      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="3" t="n">
         <v>46105</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5022,15 +4968,14 @@
       <c r="F176" t="n">
         <v>5300</v>
       </c>
-      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="3" t="n">
         <v>46105</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5049,15 +4994,14 @@
       <c r="F177" t="n">
         <v>14500</v>
       </c>
-      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="3" t="n">
         <v>46106</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5076,15 +5020,14 @@
       <c r="F178" t="n">
         <v>3500</v>
       </c>
-      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="3" t="n">
         <v>46106</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5103,15 +5046,14 @@
       <c r="F179" t="n">
         <v>0</v>
       </c>
-      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="3" t="n">
         <v>46107</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5130,15 +5072,14 @@
       <c r="F180" t="n">
         <v>4500</v>
       </c>
-      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="3" t="n">
         <v>46107</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5157,15 +5098,14 @@
       <c r="F181" t="n">
         <v>4000</v>
       </c>
-      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="3" t="n">
         <v>46108</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5184,15 +5124,14 @@
       <c r="F182" t="n">
         <v>6500</v>
       </c>
-      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="3" t="n">
         <v>46108</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5211,15 +5150,14 @@
       <c r="F183" t="n">
         <v>16000</v>
       </c>
-      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="3" t="n">
         <v>46109</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5238,15 +5176,14 @@
       <c r="F184" t="n">
         <v>0</v>
       </c>
-      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="3" t="n">
         <v>46109</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5265,15 +5202,14 @@
       <c r="F185" t="n">
         <v>0</v>
       </c>
-      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="3" t="n">
         <v>46110</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5292,15 +5228,14 @@
       <c r="F186" t="n">
         <v>0</v>
       </c>
-      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="3" t="n">
         <v>46110</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5319,15 +5254,14 @@
       <c r="F187" t="n">
         <v>0</v>
       </c>
-      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="3" t="n">
         <v>46111</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5346,15 +5280,14 @@
       <c r="F188" t="n">
         <v>6000</v>
       </c>
-      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="3" t="n">
         <v>46111</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5373,15 +5306,14 @@
       <c r="F189" t="n">
         <v>5000</v>
       </c>
-      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="3" t="n">
         <v>46112</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5400,15 +5332,14 @@
       <c r="F190" t="n">
         <v>40200</v>
       </c>
-      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="3" t="n">
         <v>46112</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5427,15 +5358,14 @@
       <c r="F191" t="n">
         <v>52700</v>
       </c>
-      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5454,15 +5384,14 @@
       <c r="F192" t="n">
         <v>0</v>
       </c>
-      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5481,15 +5410,14 @@
       <c r="F193" t="n">
         <v>0</v>
       </c>
-      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="3" t="n">
         <v>46114</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5508,15 +5436,14 @@
       <c r="F194" t="n">
         <v>2000</v>
       </c>
-      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="3" t="n">
         <v>46114</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5535,15 +5462,14 @@
       <c r="F195" t="n">
         <v>10000</v>
       </c>
-      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="3" t="n">
         <v>46115</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5562,15 +5488,14 @@
       <c r="F196" t="n">
         <v>0</v>
       </c>
-      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="3" t="n">
         <v>46115</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5589,15 +5514,14 @@
       <c r="F197" t="n">
         <v>0</v>
       </c>
-      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="3" t="n">
         <v>46116</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5616,15 +5540,14 @@
       <c r="F198" t="n">
         <v>0</v>
       </c>
-      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="3" t="n">
         <v>46116</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5643,15 +5566,14 @@
       <c r="F199" t="n">
         <v>0</v>
       </c>
-      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="3" t="n">
         <v>46117</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5670,15 +5592,14 @@
       <c r="F200" t="n">
         <v>0</v>
       </c>
-      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="3" t="n">
         <v>46117</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5697,15 +5618,14 @@
       <c r="F201" t="n">
         <v>0</v>
       </c>
-      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="3" t="n">
         <v>46118</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5724,15 +5644,14 @@
       <c r="F202" t="n">
         <v>0</v>
       </c>
-      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="3" t="n">
         <v>46118</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5751,15 +5670,14 @@
       <c r="F203" t="n">
         <v>0</v>
       </c>
-      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="3" t="n">
         <v>46119</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5783,12 +5701,12 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="3" t="n">
         <v>46119</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5812,12 +5730,12 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="3" t="n">
         <v>46120</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5841,12 +5759,12 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="3" t="n">
         <v>46120</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5870,12 +5788,12 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="3" t="n">
         <v>46121</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5899,12 +5817,12 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="3" t="n">
         <v>46121</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5928,12 +5846,12 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="3" t="n">
         <v>46122</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5957,12 +5875,12 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="3" t="n">
         <v>46122</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5986,12 +5904,12 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="3" t="n">
         <v>46123</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6015,12 +5933,12 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="3" t="n">
         <v>46123</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6044,12 +5962,12 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="3" t="n">
         <v>46124</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6073,12 +5991,12 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="3" t="n">
         <v>46124</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6102,12 +6020,12 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="3" t="n">
         <v>46125</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6120,17 +6038,14 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="3" t="n">
         <v>46125</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6143,17 +6058,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="3" t="n">
         <v>46126</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6166,17 +6078,14 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="3" t="n">
         <v>46126</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6189,17 +6098,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="3" t="n">
         <v>46127</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6212,17 +6118,14 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="3" t="n">
         <v>46127</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6235,17 +6138,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="3" t="n">
         <v>46128</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6258,17 +6158,14 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="3" t="n">
         <v>46128</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6281,17 +6178,14 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="3" t="n">
         <v>46129</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6304,17 +6198,14 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="3" t="n">
         <v>46129</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6327,15 +6218,11 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6348,15 +6235,11 @@
           <t>Diesel</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6369,9 +6252,122 @@
           <t>Petrol</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Tongatapu</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>533261</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Tongatapu</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Petrol</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>463521</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Tongatapu</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>533261</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Tongatapu</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Petrol</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>463521</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6384,43 +6380,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Fuel Type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46136</v>
+      <c r="A2" s="4" t="n">
+        <v>46107</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6434,16 +6430,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>700000</v>
+        <v>384000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46136</v>
+      <c r="A3" s="4" t="n">
+        <v>46107</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6453,20 +6449,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Petrol</t>
+          <t>Kerosene</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>150000</v>
+        <v>177800</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46155</v>
+      <c r="A4" s="4" t="n">
+        <v>46107</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6476,20 +6472,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>Petrol</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>700000</v>
+        <v>807300</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46155</v>
+      <c r="A5" s="4" t="n">
+        <v>46118</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6499,20 +6495,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Petrol</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>150000</v>
+        <v>396000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46107</v>
+      <c r="A6" s="4" t="n">
+        <v>46118</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6522,20 +6518,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>Kerosene</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>384000</v>
+        <v>292100</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46107</v>
+      <c r="A7" s="4" t="n">
+        <v>46118</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6545,66 +6541,66 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Petrol</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>807300</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pacific Energy</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tongatapu</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>556600</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pacific Energy</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tongatapu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Kerosene</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>177800</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Company 2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Tongatapu</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Petrol</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>807300</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46118</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Company 2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Tongatapu</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Diesel</t>
-        </is>
-      </c>
       <c r="E9" t="n">
-        <v>396000</v>
+        <v>254000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46118</v>
+      <c r="A10" s="4" t="n">
+        <v>46134</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6614,66 +6610,66 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Petrol</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>759000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pacific Energy</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tongatapu</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>411400</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pacific Energy</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Tongatapu</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Kerosene</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>292100</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>46118</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Company 2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Tongatapu</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Petrol</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>807300</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Company 2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Tongatapu</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Diesel</t>
-        </is>
-      </c>
       <c r="E12" t="n">
-        <v>556600</v>
+        <v>190500</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46134</v>
+      <c r="A13" s="4" t="n">
+        <v>46145</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6683,66 +6679,66 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Petrol</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>772800</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pacific Energy</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tongatapu</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>496100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pacific Energy</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tongatapu</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Kerosene</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>254000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Company 2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Tongatapu</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Petrol</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>759000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46145</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Company 2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tongatapu</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Diesel</t>
-        </is>
-      </c>
       <c r="E15" t="n">
-        <v>411400</v>
+        <v>228600</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46145</v>
+      <c r="A16" s="4" t="n">
+        <v>46158</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6752,94 +6748,94 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kerosene</t>
+          <t>Petrol</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>190500</v>
+        <v>841800</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46145</v>
+      <c r="A17" s="4" t="n">
+        <v>46115</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tongatapu</t>
+          <t>Vava'u</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Petrol</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>772800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46158</v>
+      <c r="A18" s="4" t="n">
+        <v>46115</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tongatapu</t>
+          <t>Vava'u</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>Petrol</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>496100</v>
+        <v>303600</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46158</v>
+      <c r="A19" s="4" t="n">
+        <v>46144</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tongatapu</t>
+          <t>Vava'u</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Kerosene</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228600</v>
+        <v>169400</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46158</v>
+      <c r="A20" s="4" t="n">
+        <v>46144</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tongatapu</t>
+          <t>Vava'u</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6848,16 +6844,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>841800</v>
+        <v>220800</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46115</v>
+      <c r="A21" s="4" t="n">
+        <v>46169</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6871,16 +6867,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>132000</v>
+        <v>181500</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46115</v>
+      <c r="A22" s="4" t="n">
+        <v>46169</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6894,21 +6890,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>303600</v>
+        <v>234600</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46144</v>
+      <c r="A23" s="4" t="n">
+        <v>46140</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vava'u</t>
+          <t>Tongatapu</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6917,21 +6913,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>169400</v>
+        <v>1920000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46144</v>
+      <c r="A24" s="4" t="n">
+        <v>46140</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vava'u</t>
+          <t>Tongatapu</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6940,21 +6936,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220800</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46169</v>
+      <c r="A25" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vava'u</t>
+          <t>Tongatapu</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6963,21 +6959,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>181500</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46169</v>
+      <c r="A26" s="4" t="n">
+        <v>46157</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vava'u</t>
+          <t>Tongatapu</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6986,7 +6982,53 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>234600</v>
+        <v>405000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tongatapu</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tongatapu</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Petrol</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>405000</v>
       </c>
     </row>
   </sheetData>
@@ -7004,27 +7046,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Terminal Info</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Fuel Type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
@@ -7033,7 +7075,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7058,7 +7100,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7083,7 +7125,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7108,7 +7150,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7133,7 +7175,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7158,7 +7200,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7183,7 +7225,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7208,7 +7250,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7233,7 +7275,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7258,7 +7300,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7283,7 +7325,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7308,7 +7350,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7333,7 +7375,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7358,7 +7400,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7383,7 +7425,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Company 2</t>
+          <t>Pacific Energy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7408,7 +7450,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7433,7 +7475,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7458,7 +7500,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7483,7 +7525,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7508,7 +7550,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7533,7 +7575,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Company 1</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
